--- a/606-22_ДемьянцевВВ_Лаб4.xlsx
+++ b/606-22_ДемьянцевВВ_Лаб4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vital\OneDrive\Рабочий стол\metrology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123E6542-2DE6-4CEF-9518-084F3BC6E3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8014ACE6-8945-4476-91E0-72DF152BBB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-6945" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="27">
   <si>
     <t>№</t>
   </si>
@@ -285,6 +285,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -298,9 +323,12 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx2"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -323,42 +351,19 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Лист1!$C$2</c:f>
+              <c:f>Лист1!$R$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1,5кОМ</c:v>
+                  <c:v>Замер 1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:gradFill>
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -367,84 +372,725 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Лист1!$D$1:$M$1</c:f>
+              <c:f>Лист1!$Q$10:$Q$14</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>Замер 1</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Замер 2</c:v>
+                  <c:v>56кОМ</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Замер 3</c:v>
+                  <c:v>31ГОм</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Замер 4</c:v>
+                  <c:v>5,1кОМ</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Замер 5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Замер 6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Замер 7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Замер 8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Замер 9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Замер 10</c:v>
+                  <c:v>10кОМ</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Лист1!$D$2:$M$2</c:f>
+              <c:f>Лист1!$R$10:$R$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>1.54</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.53</c:v>
-                </c:pt>
-                <c:pt idx="2" formatCode="0.00">
-                  <c:v>1.52</c:v>
+                  <c:v>-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.5</c:v>
+                  <c:v>-9.9999999999999645E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.49</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.51</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.48</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.52</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.47</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8781-4373-8744-4F5248FF5AF4}"/>
+              <c16:uniqueId val="{00000000-959E-4FEA-A769-116CC92A4212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$S$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$10:$Q$14</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$S$10:$S$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.0000000000000018E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.79999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.19999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.9999999999999574E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-959E-4FEA-A769-116CC92A4212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$T$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$10:$Q$14</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$T$10:$T$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-2.0000000000000018E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.19999999999999929</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-959E-4FEA-A769-116CC92A4212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$U$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$10:$Q$14</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$U$10:$U$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-1.0000000000000009E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.2000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.10000000000000053</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.9999999999999645E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-959E-4FEA-A769-116CC92A4212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$V$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$10:$Q$14</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$V$10:$V$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.0000000000000009E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.29999999999999982</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-9.9999999999999645E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-959E-4FEA-A769-116CC92A4212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$W$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$10:$Q$14</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$W$10:$W$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-9.9999999999999645E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-959E-4FEA-A769-116CC92A4212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$X$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$10:$Q$14</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$X$10:$X$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3.0000000000000027E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.9999999999999645E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-959E-4FEA-A769-116CC92A4212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$Y$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$10:$Q$14</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$Y$10:$Y$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-3.0000000000000027E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.89999999999999858</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-9.9999999999999645E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.30000000000000071</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-959E-4FEA-A769-116CC92A4212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$Z$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$10:$Q$14</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$Z$10:$Z$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.19999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.19999999999999929</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-959E-4FEA-A769-116CC92A4212}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$AA$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$10:$Q$14</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$AA$10:$AA$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.0000000000000018E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.2000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.10000000000000053</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-959E-4FEA-A769-116CC92A4212}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -456,13 +1102,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="100"/>
-        <c:overlap val="-24"/>
-        <c:axId val="2051801247"/>
-        <c:axId val="2051795007"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1644965247"/>
+        <c:axId val="1644969087"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2051801247"/>
+        <c:axId val="1644965247"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -476,7 +1122,7 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx2">
+              <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
                 <a:lumOff val="85000"/>
               </a:schemeClr>
@@ -492,7 +1138,10 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx2"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -502,7 +1151,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2051795007"/>
+        <c:crossAx val="1644969087"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -510,7 +1159,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2051795007"/>
+        <c:axId val="1644969087"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -520,7 +1169,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx2">
+                <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -548,7 +1197,10 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx2"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -558,7 +1210,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2051801247"/>
+        <c:crossAx val="1644965247"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -570,6 +1222,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -580,7 +1263,972 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx2">
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$R$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$2:$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$2:$R$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4.0000000000000036E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.79999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.9999999999999361E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.30000000000000071</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3F51-4364-A3BE-4FDED69B7DF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$S$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$2:$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$S$2:$S$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3.0000000000000027E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-6.9999999999999396E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.19999999999999929</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3F51-4364-A3BE-4FDED69B7DF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$T$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$2:$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$T$2:$T$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.0000000000000018E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.79999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.19999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15000000000000036</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3F51-4364-A3BE-4FDED69B7DF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$U$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$2:$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$U$2:$U$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.1800000000000006</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.40000000000000036</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3F51-4364-A3BE-4FDED69B7DF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$V$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$2:$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$V$2:$V$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-1.0000000000000009E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-6.9999999999999396E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.38000000000000078</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-3F51-4364-A3BE-4FDED69B7DF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$W$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$2:$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$W$2:$W$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.0000000000000009E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.79999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0000000000000462E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.22000000000000064</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-3F51-4364-A3BE-4FDED69B7DF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$X$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$2:$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$X$2:$X$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-2.0000000000000018E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-9.9999999999999645E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.3100000000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-3F51-4364-A3BE-4FDED69B7DF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$Y$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$2:$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$Y$2:$Y$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.79999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.11999999999999922</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.26999999999999957</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-3F51-4364-A3BE-4FDED69B7DF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$Z$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$2:$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$Z$2:$Z$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.0000000000000018E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.0000000000000071E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.17999999999999972</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-3F51-4364-A3BE-4FDED69B7DF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$AA$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Q$2:$Q$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1,5кОМ</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56кОМ</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31ГОм</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5,1кОМ</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10кОМ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$AA$2:$AA$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-3.0000000000000027E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.0000000000000036E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.34999999999999964</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-3F51-4364-A3BE-4FDED69B7DF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1684891423"/>
+        <c:axId val="1684887103"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1684891423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1684887103"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1684887103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1684891423"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -647,28 +2295,74 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="207">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -683,7 +2377,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -691,7 +2385,7 @@
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -699,14 +2393,17 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
@@ -715,8 +2412,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk2">
-        <a:lumMod val="75000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
@@ -739,35 +2437,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="31750" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -776,32 +2474,33 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt2"/>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="2"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -817,16 +2516,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -860,17 +2564,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -879,14 +2583,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -898,20 +2602,26 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -925,99 +2635,96 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -1025,17 +2732,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="dash"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -1044,9 +2751,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -1055,14 +2765,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDash"/>
+        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -1071,7 +2781,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
@@ -1080,7 +2793,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -1101,7 +2814,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -1110,8 +2826,517 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -1120,23 +3345,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>447674</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>184896</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>76199</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>521073</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>43702</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Диаграмма 1">
+        <xdr:cNvPr id="4" name="Диаграмма 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{066B26B7-A5A1-583D-C679-D3F0E1DFC46A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A962645-38FE-9A43-7503-E29C851F927B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1149,6 +3374,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Диаграмма 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B200D08D-524C-A428-31CD-F26683D7B184}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1355,7 +3616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1364,7 +3625,7 @@
     <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1404,8 +3665,47 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1445,8 +3745,57 @@
       <c r="M2">
         <v>1.47</v>
       </c>
+      <c r="O2" s="2">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="2">
+        <f>D2-1.5</f>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="S2" s="2">
+        <f>E2-1.5</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="T2" s="2">
+        <f t="shared" ref="S2:AA2" si="0">F2-1.5</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="U2" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V2" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.0000000000000009E-2</v>
+      </c>
+      <c r="W2" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="X2" s="2">
+        <f t="shared" si="0"/>
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="Y2" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2">
+        <f t="shared" si="0"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AA2" s="2">
+        <f t="shared" si="0"/>
+        <v>-3.0000000000000027E-2</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1486,8 +3835,57 @@
       <c r="M3">
         <v>57.8</v>
       </c>
+      <c r="O3" s="2">
+        <v>2</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" s="2">
+        <f>D3-56</f>
+        <v>0.79999999999999716</v>
+      </c>
+      <c r="S3" s="2">
+        <f t="shared" ref="S3:AA3" si="1">E3-56</f>
+        <v>2</v>
+      </c>
+      <c r="T3" s="2">
+        <f t="shared" si="1"/>
+        <v>0.79999999999999716</v>
+      </c>
+      <c r="U3" s="2">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="V3" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.5</v>
+      </c>
+      <c r="W3" s="2">
+        <f t="shared" si="1"/>
+        <v>0.79999999999999716</v>
+      </c>
+      <c r="X3" s="2">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Y3" s="2">
+        <f t="shared" si="1"/>
+        <v>0.79999999999999716</v>
+      </c>
+      <c r="Z3" s="2">
+        <f t="shared" si="1"/>
+        <v>-1.5</v>
+      </c>
+      <c r="AA3" s="2">
+        <f t="shared" si="1"/>
+        <v>1.7999999999999972</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1497,38 +3895,27 @@
       <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4">
-        <v>0.31</v>
-      </c>
-      <c r="E4">
-        <v>0.32</v>
-      </c>
-      <c r="F4">
-        <v>0.33</v>
-      </c>
-      <c r="G4">
-        <v>0.34</v>
-      </c>
-      <c r="H4">
-        <v>0.31</v>
-      </c>
-      <c r="I4">
-        <v>0.33</v>
-      </c>
-      <c r="J4">
-        <v>0.31</v>
-      </c>
-      <c r="K4">
-        <v>0.33</v>
-      </c>
-      <c r="L4">
-        <v>0.32</v>
-      </c>
-      <c r="M4">
-        <v>0.3</v>
-      </c>
+      <c r="O4" s="2">
+        <v>3</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1568,8 +3955,57 @@
       <c r="M5">
         <v>5.0599999999999996</v>
       </c>
+      <c r="O5" s="2">
+        <v>4</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R5" s="2">
+        <f>D5-5.1</f>
+        <v>-2.9999999999999361E-2</v>
+      </c>
+      <c r="S5" s="2">
+        <f t="shared" ref="S5:AA5" si="2">E5-5.1</f>
+        <v>-6.9999999999999396E-2</v>
+      </c>
+      <c r="T5" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.19999999999999929</v>
+      </c>
+      <c r="U5" s="2">
+        <f t="shared" si="2"/>
+        <v>0.1800000000000006</v>
+      </c>
+      <c r="V5" s="2">
+        <f t="shared" si="2"/>
+        <v>-6.9999999999999396E-2</v>
+      </c>
+      <c r="W5" s="2">
+        <f t="shared" si="2"/>
+        <v>2.0000000000000462E-2</v>
+      </c>
+      <c r="X5" s="2">
+        <f t="shared" si="2"/>
+        <v>-9.9999999999999645E-2</v>
+      </c>
+      <c r="Y5" s="2">
+        <f t="shared" si="2"/>
+        <v>-0.11999999999999922</v>
+      </c>
+      <c r="Z5" s="2">
+        <f t="shared" si="2"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AA5" s="2">
+        <f t="shared" si="2"/>
+        <v>-4.0000000000000036E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1609,8 +4045,57 @@
       <c r="M6">
         <v>10.35</v>
       </c>
+      <c r="O6" s="2">
+        <v>5</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R6" s="2">
+        <f>D6-10</f>
+        <v>0.30000000000000071</v>
+      </c>
+      <c r="S6" s="2">
+        <f t="shared" ref="S6:AA6" si="3">E6-10</f>
+        <v>0.19999999999999929</v>
+      </c>
+      <c r="T6" s="2">
+        <f t="shared" si="3"/>
+        <v>0.15000000000000036</v>
+      </c>
+      <c r="U6" s="2">
+        <f t="shared" si="3"/>
+        <v>0.40000000000000036</v>
+      </c>
+      <c r="V6" s="2">
+        <f t="shared" si="3"/>
+        <v>0.38000000000000078</v>
+      </c>
+      <c r="W6" s="2">
+        <f t="shared" si="3"/>
+        <v>0.22000000000000064</v>
+      </c>
+      <c r="X6" s="2">
+        <f t="shared" si="3"/>
+        <v>0.3100000000000005</v>
+      </c>
+      <c r="Y6" s="2">
+        <f t="shared" si="3"/>
+        <v>0.26999999999999957</v>
+      </c>
+      <c r="Z6" s="2">
+        <f t="shared" si="3"/>
+        <v>0.17999999999999972</v>
+      </c>
+      <c r="AA6" s="2">
+        <f t="shared" si="3"/>
+        <v>0.34999999999999964</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
@@ -1650,8 +4135,47 @@
       <c r="M9" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="O9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>1</v>
       </c>
@@ -1691,8 +4215,57 @@
       <c r="M10" s="2">
         <v>1.52</v>
       </c>
+      <c r="O10" s="2">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R10" s="2">
+        <f>D10-1.5</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <f>E10-1.5</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="T10" s="2">
+        <f t="shared" ref="T10" si="4">F10-1.5</f>
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="U10" s="2">
+        <f t="shared" ref="U10" si="5">G10-1.5</f>
+        <v>-1.0000000000000009E-2</v>
+      </c>
+      <c r="V10" s="2">
+        <f t="shared" ref="V10" si="6">H10-1.5</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="W10" s="2">
+        <f t="shared" ref="W10" si="7">I10-1.5</f>
+        <v>0</v>
+      </c>
+      <c r="X10" s="2">
+        <f t="shared" ref="X10" si="8">J10-1.5</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="Y10" s="2">
+        <f t="shared" ref="Y10" si="9">K10-1.5</f>
+        <v>-3.0000000000000027E-2</v>
+      </c>
+      <c r="Z10" s="2">
+        <f t="shared" ref="Z10" si="10">L10-1.5</f>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2">
+        <f t="shared" ref="AA10" si="11">M10-1.5</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>2</v>
       </c>
@@ -1732,8 +4305,57 @@
       <c r="M11" s="2">
         <v>54.8</v>
       </c>
+      <c r="O11" s="2">
+        <v>2</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R11" s="2">
+        <f>D11-56</f>
+        <v>-2</v>
+      </c>
+      <c r="S11" s="2">
+        <f t="shared" ref="S11" si="12">E11-56</f>
+        <v>-0.79999999999999716</v>
+      </c>
+      <c r="T11" s="2">
+        <f t="shared" ref="T11" si="13">F11-56</f>
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <f t="shared" ref="U11" si="14">G11-56</f>
+        <v>-1.2000000000000028</v>
+      </c>
+      <c r="V11" s="2">
+        <f t="shared" ref="V11" si="15">H11-56</f>
+        <v>0.20000000000000284</v>
+      </c>
+      <c r="W11" s="2">
+        <f t="shared" ref="W11" si="16">I11-56</f>
+        <v>-0.5</v>
+      </c>
+      <c r="X11" s="2">
+        <f t="shared" ref="X11" si="17">J11-56</f>
+        <v>-1</v>
+      </c>
+      <c r="Y11" s="2">
+        <f t="shared" ref="Y11" si="18">K11-56</f>
+        <v>-0.89999999999999858</v>
+      </c>
+      <c r="Z11" s="2">
+        <f t="shared" ref="Z11" si="19">L11-56</f>
+        <v>-0.5</v>
+      </c>
+      <c r="AA11" s="2">
+        <f t="shared" ref="AA11" si="20">M11-56</f>
+        <v>-1.2000000000000028</v>
+      </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>3</v>
       </c>
@@ -1753,8 +4375,27 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
+      <c r="O12" s="2">
+        <v>3</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>4</v>
       </c>
@@ -1794,8 +4435,57 @@
       <c r="M13" s="2">
         <v>5.2</v>
       </c>
+      <c r="O13" s="2">
+        <v>4</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R13" s="2">
+        <f>D13-5.1</f>
+        <v>-9.9999999999999645E-2</v>
+      </c>
+      <c r="S13" s="2">
+        <f t="shared" ref="S13" si="21">E13-5.1</f>
+        <v>-0.19999999999999929</v>
+      </c>
+      <c r="T13" s="2">
+        <f t="shared" ref="T13" si="22">F13-5.1</f>
+        <v>0</v>
+      </c>
+      <c r="U13" s="2">
+        <f t="shared" ref="U13" si="23">G13-5.1</f>
+        <v>0.10000000000000053</v>
+      </c>
+      <c r="V13" s="2">
+        <f t="shared" ref="V13" si="24">H13-5.1</f>
+        <v>-0.29999999999999982</v>
+      </c>
+      <c r="W13" s="2">
+        <f t="shared" ref="W13" si="25">I13-5.1</f>
+        <v>-9.9999999999999645E-2</v>
+      </c>
+      <c r="X13" s="2">
+        <f t="shared" ref="X13" si="26">J13-5.1</f>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="2">
+        <f t="shared" ref="Y13" si="27">K13-5.1</f>
+        <v>-9.9999999999999645E-2</v>
+      </c>
+      <c r="Z13" s="2">
+        <f t="shared" ref="Z13" si="28">L13-5.1</f>
+        <v>-0.19999999999999929</v>
+      </c>
+      <c r="AA13" s="2">
+        <f t="shared" ref="AA13" si="29">M13-5.1</f>
+        <v>0.10000000000000053</v>
+      </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>5</v>
       </c>
@@ -1834,6 +4524,55 @@
       </c>
       <c r="M14" s="2">
         <v>10</v>
+      </c>
+      <c r="O14" s="2">
+        <v>5</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R14" s="2">
+        <f>D14-10</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <f t="shared" ref="S14" si="30">E14-10</f>
+        <v>-1.9999999999999574E-2</v>
+      </c>
+      <c r="T14" s="2">
+        <f t="shared" ref="T14" si="31">F14-10</f>
+        <v>0.19999999999999929</v>
+      </c>
+      <c r="U14" s="2">
+        <f t="shared" ref="U14" si="32">G14-10</f>
+        <v>9.9999999999999645E-2</v>
+      </c>
+      <c r="V14" s="2">
+        <f t="shared" ref="V14" si="33">H14-10</f>
+        <v>-9.9999999999999645E-2</v>
+      </c>
+      <c r="W14" s="2">
+        <f t="shared" ref="W14" si="34">I14-10</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="2">
+        <f t="shared" ref="X14" si="35">J14-10</f>
+        <v>9.9999999999999645E-2</v>
+      </c>
+      <c r="Y14" s="2">
+        <f t="shared" ref="Y14" si="36">K14-10</f>
+        <v>0.30000000000000071</v>
+      </c>
+      <c r="Z14" s="2">
+        <f t="shared" ref="Z14" si="37">L14-10</f>
+        <v>0.19999999999999929</v>
+      </c>
+      <c r="AA14" s="2">
+        <f t="shared" ref="AA14" si="38">M14-10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1899,23 +4638,23 @@
         <v>2</v>
       </c>
       <c r="B21" s="8" t="str">
-        <f t="shared" ref="B21:B24" si="0">C3</f>
+        <f t="shared" ref="B21:B24" si="39">C3</f>
         <v>56кОМ</v>
       </c>
       <c r="C21" s="9">
-        <f t="shared" ref="C21:C24" si="1">AVERAGE(D3:M3)</f>
+        <f t="shared" ref="C21:C24" si="40">AVERAGE(D3:M3)</f>
         <v>56.65</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" ref="D21:D24" si="2">_xlfn.STDEV.S(D3:M3)/SQRT(COUNT(D3:M3))</f>
+        <f t="shared" ref="D21:D24" si="41">_xlfn.STDEV.S(D3:M3)/SQRT(COUNT(D3:M3))</f>
         <v>0.39895697345286063</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" ref="E21:E24" si="3">AVERAGE(D11:M11)</f>
+        <f t="shared" ref="E21:E24" si="42">AVERAGE(D11:M11)</f>
         <v>55.21</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" ref="F21:F23" si="4">_xlfn.STDEV.S(D11:M11)/SQRT(COUNT(D11:M11))</f>
+        <f t="shared" ref="F21:F23" si="43">_xlfn.STDEV.S(D11:M11)/SQRT(COUNT(D11:M11))</f>
         <v>0.20080393975772068</v>
       </c>
     </row>
@@ -1924,48 +4663,36 @@
         <v>3</v>
       </c>
       <c r="B22" s="8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="39"/>
         <v>31ГОм</v>
       </c>
-      <c r="C22" s="9">
-        <f t="shared" si="1"/>
-        <v>0.31999999999999995</v>
-      </c>
-      <c r="D22" s="9">
-        <f t="shared" si="2"/>
-        <v>3.9440531887330807E-3</v>
-      </c>
-      <c r="E22" s="9" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F22" s="9" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>4</v>
       </c>
       <c r="B23" s="8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="39"/>
         <v>5,1кОМ</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="40"/>
         <v>5.0650000000000013</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="41"/>
         <v>3.3936214677931668E-2</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="42"/>
         <v>5.0200000000000005</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="43"/>
         <v>4.163331998932264E-2</v>
       </c>
     </row>
@@ -1974,19 +4701,19 @@
         <v>5</v>
       </c>
       <c r="B24" s="8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="39"/>
         <v>10кОМ</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="40"/>
         <v>10.276</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="41"/>
         <v>2.7373953556863798E-2</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="42"/>
         <v>10.077999999999999</v>
       </c>
       <c r="F24" s="9">
